--- a/Retailer_Summary.xlsx
+++ b/Retailer_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,2294 +455,2293 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2002095</v>
+        <v>2002054</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Savala Agencies</t>
+          <t>Hariom Traders (Bhayander)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200205300429</v>
+        <v>200205400151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mahavir sweet Corner</t>
+          <t>Suraksha Medical</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="G2" t="n">
-        <v>41.80709333333333</v>
+        <v>73.28138666666668</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2002057</v>
+        <v>2002054</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Supreme Traders (Badlapur)</t>
+          <t>Hariom Traders (Bhayander)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200205700151</v>
+        <v>200205400414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Kohinoor Grahak Bazar</t>
+          <t>New Low Prise Super market</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SHUBHANGI RAIKWAR</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>19.66666666666667</v>
+        <v>29.66666666666667</v>
       </c>
       <c r="G3" t="n">
-        <v>28.76989666666667</v>
+        <v>167.4795133333334</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2002057</v>
+        <v>2002061</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Supreme Traders (Badlapur)</t>
+          <t>Unique Agencies</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200205700384</v>
+        <v>200206100061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PRAGATI SUPER MKT.</t>
+          <t>MATAJI SUPER MARKET(SOYAL )</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SHUBHANGI RAIKWAR</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>20.66666666666667</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="G4" t="n">
-        <v>27.05408666666667</v>
+        <v>21.55905</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2011731</v>
+        <v>2002061</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sandeep Stores</t>
+          <t>Unique Agencies</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200205700568</v>
+        <v>200206100183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Shree Mahakali Super Market</t>
+          <t>AAIJI SUPER MARKET</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SHUBHANGI RAIKWAR</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="G5" t="n">
-        <v>101.9920266666667</v>
+        <v>25.25886333333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2002057</v>
+        <v>2002061</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Supreme Traders (Badlapur)</t>
+          <t>Unique Agencies</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200205700596</v>
+        <v>200206100184</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B Mart</t>
+          <t>KANAIYA  SUPER MARKET</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SHUBHANGI RAIKWAR</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>64.33333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>38.77142</v>
+        <v>69.77296666666666</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
+      <c r="A7" t="n">
+        <v>2002061</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Unique Agencies</t>
+        </is>
+      </c>
       <c r="C7" t="n">
-        <v>200205700618</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+        <v>200206100265</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RAMDEV SUPER MART</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>VINAYAK VIJAY PATIL</t>
+        </is>
+      </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="G7" t="n">
-        <v>9.672739999999999</v>
+        <v>89.50529666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2002060</v>
+        <v>2002061</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hitesh Enterprise (Uran)</t>
+          <t>Unique Agencies</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>200206000005</v>
+        <v>200206100277</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CHARBHUJA  DRY</t>
+          <t>A G SUPER MARKET</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>13.33333333333333</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>55.74277666666666</v>
+        <v>83.96005666666667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2002060</v>
+        <v>2002061</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hitesh Enterprise (Uran)</t>
+          <t>Unique Agencies</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>200206000006</v>
+        <v>200206100345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PAREKH STORES</t>
+          <t>AMARDEEP GENERAL STORES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>14.66666666666667</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
-        <v>31.40123333333334</v>
+        <v>143.0090633333333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2002060</v>
+        <v>2002061</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hitesh Enterprise (Uran)</t>
+          <t>Unique Agencies</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>200206000020</v>
+        <v>200206100364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GANESH PRO STORE</t>
+          <t>MAATAJI DHANYA BHANDAR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>50.66666666666666</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>345.4742133333334</v>
+        <v>17.85333666666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2002060</v>
+        <v>2002061</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hitesh Enterprise (Uran)</t>
+          <t>Unique Agencies</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>200206000044</v>
+        <v>200206100887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>URAN TALUKA GRAHAK SAHKARI S M</t>
+          <t>GET WELL CHEMIST</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>31.33333333333333</v>
       </c>
       <c r="G11" t="n">
-        <v>93.09971666666667</v>
+        <v>39.20676333333333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2002060</v>
+        <v>2002061</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hitesh Enterprise (Uran)</t>
+          <t>Unique Agencies</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>200206000046</v>
+        <v>200206100984</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TRIMURTI D/F</t>
+          <t>RAJ SUPER MARKET</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>34.66666666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>200.62471</v>
+        <v>34.95543666666666</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2002060</v>
+        <v>2002061</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hitesh Enterprise (Uran)</t>
+          <t>Unique Agencies</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>200206000047</v>
+        <v>200206101134</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SHREE TIRUPATI D/F</t>
+          <t>HR SUPER MARKET</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>34.33333333333334</v>
+        <v>43.66666666666666</v>
       </c>
       <c r="G13" t="n">
-        <v>171.3441033333334</v>
+        <v>47.30720666666667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2002060</v>
+        <v>2002062</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hitesh Enterprise (Uran)</t>
+          <t>Hari Om Traders (Boisar)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>200206000084</v>
+        <v>200206200010</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NEW DAILY MART</t>
+          <t>Gayatri Traders</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>47.33333333333334</v>
+        <v>64</v>
       </c>
       <c r="G14" t="n">
-        <v>181.2304066666667</v>
+        <v>240.0212333333334</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2002060</v>
+        <v>2002062</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hitesh Enterprise (Uran)</t>
+          <t>Hari Om Traders (Boisar)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>200206000087</v>
+        <v>200206200037</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BEST DRYFRUITS</t>
+          <t>New brijawasi super market</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>33.66666666666666</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>58.09981666666666</v>
+        <v>101.6890833333333</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2002060</v>
+        <v>2002062</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hitesh Enterprise (Uran)</t>
+          <t>Hari Om Traders (Boisar)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>200206000101</v>
+        <v>200206200041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TIPTOP SUPERMARKET</t>
+          <t>A One home stores</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>122.7412966666667</v>
+        <v>129.8950833333333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2018993</v>
+        <v>2002062</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SRI ENTERPRISES</t>
+          <t>Hari Om Traders (Boisar)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>200206700008</v>
+        <v>200206200076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Daily Needs (CBD)</t>
+          <t>New Mamaji Gen Store</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>19.66666666666667</v>
+        <v>20.33333333333333</v>
       </c>
       <c r="G17" t="n">
-        <v>66.66565333333334</v>
+        <v>76.59288666666666</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2022939</v>
+        <v>2002062</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>Hari Om Traders (Boisar)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>200206700482</v>
+        <v>200206200255</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FOOD BASKET</t>
+          <t>C-MART</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>43.66666666666666</v>
       </c>
       <c r="G18" t="n">
-        <v>133.8716033333334</v>
+        <v>76.90856666666666</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2022939</v>
+        <v>2002062</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>Hari Om Traders (Boisar)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>200206700519</v>
+        <v>200206200518</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KOHINOOR SUPER MARKET</t>
+          <t>SHREE SAMRTH KRUPA SUPER MARKET</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>45.33333333333334</v>
+        <v>33</v>
       </c>
       <c r="G19" t="n">
-        <v>68.79257333333332</v>
+        <v>61.81890333333333</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2002070</v>
+        <v>2002062</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Harihar Agencies</t>
+          <t>Hari Om Traders (Boisar)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>200207000230</v>
+        <v>200206200702</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sunita Sweet Mart</t>
+          <t>THE FAMAILY BAZZAR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SHUBHANGI RAIKWAR</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>24.33333333333333</v>
+        <v>47</v>
       </c>
       <c r="G20" t="n">
-        <v>663.5676500000001</v>
+        <v>83.82443666666667</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2002070</v>
+        <v>2018129</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Harihar Agencies</t>
+          <t>SASMI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>200207001063</v>
+        <v>200207400046</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SATYAM SUPER MARKET</t>
+          <t>Dedhia Stores (Supermarket)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SHUBHANGI RAIKWAR</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>29.33333333333333</v>
+        <v>54.33333333333334</v>
       </c>
       <c r="G21" t="n">
-        <v>52.05216333333333</v>
+        <v>172.53675</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2002070</v>
+        <v>2021259</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Harihar Agencies</t>
+          <t>WADEKAR TRADERS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>200207001140</v>
+        <v>200207400215</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SATNAM STORE</t>
+          <t>Narendra Kirana Store</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SHUBHANGI RAIKWAR</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>28.66666666666667</v>
+        <v>34</v>
       </c>
       <c r="G22" t="n">
-        <v>111.7789166666667</v>
+        <v>32.27006333333333</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2022639</v>
+        <v>2021259</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shivani Enterprises</t>
+          <t>WADEKAR TRADERS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>200207300206</v>
+        <v>200207400241</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KOHINOOR S/M</t>
+          <t>MOMAIYA LOW PRICE PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>JOSHUA SHAJI FRANCIS</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>30</v>
+        <v>31.33333333333333</v>
       </c>
       <c r="G23" t="n">
-        <v>70.16096333333333</v>
+        <v>88.12483333333334</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2022639</v>
+        <v>2018129</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shivani Enterprises</t>
+          <t>SASMI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>200207300363</v>
+        <v>200207400392</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BIPIN S/M</t>
+          <t>Rishi Dairy</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JOSHUA SHAJI FRANCIS</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>24.33333333333333</v>
+        <v>37.33333333333334</v>
       </c>
       <c r="G24" t="n">
-        <v>76.35146999999999</v>
+        <v>37.61322</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2022639</v>
+        <v>2018129</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shivani Enterprises</t>
+          <t>SASMI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>200207300368</v>
+        <v>200207400412</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DIMAND GEN.</t>
+          <t>Ravi Stores</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>JOSHUA SHAJI FRANCIS</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>15.33333333333333</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="G25" t="n">
-        <v>29.14807333333333</v>
+        <v>47.47641333333333</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2009842</v>
+        <v>2018129</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R. P. Agency</t>
+          <t>SASMI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>200209500038</v>
+        <v>200207400696</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SHIWAM SUPER MARKET</t>
+          <t>Ambika STATIONERY /PROVISION STORE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>66.66666666666667</v>
+        <v>45.33333333333334</v>
       </c>
       <c r="G26" t="n">
-        <v>47.29138666666666</v>
+        <v>39.31311333333334</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2002095</v>
+        <v>2018129</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Savala Agencies</t>
+          <t>SASMI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>200209500324</v>
+        <v>200207400703</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Dattatraya D/f  Gen.Store</t>
+          <t>Balaji Supermarket</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>17.33333333333333</v>
+        <v>33.66666666666666</v>
       </c>
       <c r="G27" t="n">
-        <v>25.95256666666667</v>
+        <v>19.41423666666667</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2002095</v>
+        <v>2018129</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Savala Agencies</t>
+          <t>SASMI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>200209501067</v>
+        <v>200207400731</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Rane Bandhu</t>
+          <t>Om Supermarket</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>15.66666666666667</v>
+        <v>21.33333333333333</v>
       </c>
       <c r="G28" t="n">
-        <v>34.00460333333334</v>
+        <v>18.94382666666667</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2002095</v>
+        <v>2018129</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Savala Agencies</t>
+          <t>SASMI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>200209501160</v>
+        <v>200207400750</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Jivdani Dugdhalaya</t>
+          <t>Janta SuperMarket</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="G29" t="n">
-        <v>52.10580000000001</v>
+        <v>20.73424666666667</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2002095</v>
+        <v>2018129</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Savala Agencies</t>
+          <t>SASMI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>200209501162</v>
+        <v>200207401236</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ali Gen Store</t>
+          <t>AAYUSH SUPER MARKET</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>36.33333333333334</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="G30" t="n">
-        <v>52.83083666666666</v>
+        <v>36.78348</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2023085</v>
+        <v>2018129</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>N T Distributors</t>
+          <t>SASMI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>200405300324</v>
+        <v>200207401317</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Food Mart</t>
+          <t>SHREE  APNA  BAZAR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UDAY DILIP INDALKAR</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>36</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="G31" t="n">
-        <v>98.51073333333333</v>
+        <v>25.45146333333333</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2023085</v>
+        <v>2011866</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>N T Distributors</t>
+          <t>Sainath Enterprises</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>200405300624</v>
+        <v>200208200074</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DAILY NEEDS ENTERPRISES-2</t>
+          <t>New Krishna Super Market</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UDAY DILIP INDALKAR</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>45.66666666666666</v>
+        <v>12.33333333333333</v>
       </c>
       <c r="G32" t="n">
-        <v>208.18544</v>
+        <v>9.410486666666666</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2022939</v>
+        <v>2011866</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>Sainath Enterprises</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>200511800890</v>
+        <v>200208200088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mahadev dairy</t>
+          <t>MARKET POINT  NO-3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>16.33333333333333</v>
+        <v>75</v>
       </c>
       <c r="G33" t="n">
-        <v>107.8869266666667</v>
+        <v>450.8839566666666</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2005118</v>
+        <v>2011866</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A1 DISTRIBUTOR</t>
+          <t>Sainath Enterprises</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>200511801044</v>
+        <v>200208200185</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DG MALL</t>
+          <t>MARKET POINT NO-01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ROHAN SINGH</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>22</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="G34" t="n">
-        <v>91.87452999999999</v>
+        <v>206.2826733333333</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2023002</v>
+        <v>2011866</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nimse Trading Company</t>
+          <t>Sainath Enterprises</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>200625400127</v>
+        <v>200208200207</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OM SUP. MARKET</t>
+          <t>Monika Traders</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AMIT SANJEEV PANDEY</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>13.66666666666667</v>
+        <v>31.33333333333333</v>
       </c>
       <c r="G35" t="n">
-        <v>65.54083333333334</v>
+        <v>49.71701000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2023823</v>
+        <v>2011866</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ashtavinayak Agencies</t>
+          <t>Sainath Enterprises</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>200625400735</v>
+        <v>200208200267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ROYAL SUPER MARKET</t>
+          <t>MAX MALL-2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AMIT SANJEEV PANDEY</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>15</v>
+        <v>72.66666666666667</v>
       </c>
       <c r="G36" t="n">
-        <v>35.51502</v>
+        <v>195.0510733333333</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2005118</v>
+        <v>2011866</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A1 DISTRIBUTOR</t>
+          <t>Sainath Enterprises</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>200660400395</v>
+        <v>200208200308</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KALWA SUPER MKT PVT LTD</t>
+          <t>MARKET POINT-NO-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ROHAN SINGH</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>21</v>
+        <v>69.66666666666667</v>
       </c>
       <c r="G37" t="n">
-        <v>29.01681666666667</v>
+        <v>185.4611633333334</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2022639</v>
+        <v>2009155</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Shivani Enterprises</t>
+          <t>BABULAL JAYANTILAL &amp; CO.</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>200923800009</v>
+        <v>200515600007</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DARSHAN BISCUITS</t>
+          <t>Sahyog Bakery</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>JOSHUA SHAJI FRANCIS</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>21.66666666666667</v>
+        <v>34</v>
       </c>
       <c r="G38" t="n">
-        <v>316.9292133333333</v>
+        <v>54.24141333333333</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2009842</v>
+        <v>2009155</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R. P. Agency</t>
+          <t>BABULAL JAYANTILAL &amp; CO.</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>200984200153</v>
+        <v>200515600226</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SAI PRASAD DRY FRUIT</t>
+          <t>Anand Society General Stores</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>45</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="G39" t="n">
-        <v>40.93277333333334</v>
+        <v>44.60763666666666</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2009842</v>
+        <v>2009155</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R. P. Agency</t>
+          <t>BABULAL JAYANTILAL &amp; CO.</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>200984200845</v>
+        <v>200515600264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>WELCOME STORE</t>
+          <t>Mayur Masala Super Market</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>27.66666666666667</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="G40" t="n">
-        <v>34.67592666666667</v>
+        <v>92.47462333333333</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2009842</v>
+        <v>2009155</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R. P. Agency</t>
+          <t>BABULAL JAYANTILAL &amp; CO.</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>200984201066</v>
+        <v>200515600453</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ADIMAYA ENTERPRISES</t>
+          <t>METRO SUPER MARKET</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>32.33333333333334</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="G41" t="n">
-        <v>35.94880333333333</v>
+        <v>62.37947333333333</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2023085</v>
+        <v>2016798</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>N T Distributors</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>201063400142</v>
+        <v>200607200077</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TOWN BAZAAR</t>
+          <t>HARIOM SUPER BAZAR</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UDAY DILIP INDALKAR</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>28.33333333333333</v>
+        <v>30.33333333333333</v>
       </c>
       <c r="G42" t="n">
-        <v>92.34347000000001</v>
+        <v>37.56862333333333</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2023085</v>
+        <v>2016798</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>N T Distributors</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>201063400275</v>
+        <v>200607200223</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FOOD BASKET HK</t>
+          <t>GUPTA PROVISION STORE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UDAY DILIP INDALKAR</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>40</v>
+        <v>29.66666666666667</v>
       </c>
       <c r="G43" t="n">
-        <v>102.4090866666667</v>
+        <v>25.20131</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2023002</v>
+        <v>2016798</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nimse Trading Company</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>201074800326</v>
+        <v>200607200227</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Uma General Store</t>
+          <t>ANIL COLDRINK</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AMIT SANJEEV PANDEY</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G44" t="n">
-        <v>30.98505666666667</v>
+        <v>12.17439333333333</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2023002</v>
+        <v>2016798</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nimse Trading Company</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>201074800404</v>
+        <v>200607200713</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GURU KRIPA DAIRY  COLD DRINKS</t>
+          <t>JANNAT MEDICAL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AMIT SANJEEV PANDEY</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>12.33333333333333</v>
+        <v>30</v>
       </c>
       <c r="G45" t="n">
-        <v>56.46564333333333</v>
+        <v>20.32688666666667</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2011731</v>
+        <v>2016798</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sandeep Stores</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>201173100172</v>
+        <v>200607200760</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SHREE SADGURU KRUPA (NEW )</t>
+          <t>KARARI MART</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SHUBHANGI RAIKWAR</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>20.66666666666667</v>
+        <v>40.66666666666666</v>
       </c>
       <c r="G46" t="n">
-        <v>75.18834</v>
+        <v>116.9811733333333</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2011731</v>
+        <v>2016798</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sandeep Stores</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>201173100249</v>
+        <v>200607200861</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ROYAL SUPER MARKET</t>
+          <t>JAY GANESH S/M</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SHUBHANGI RAIKWAR</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>30.66666666666667</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="G47" t="n">
-        <v>140.0387133333333</v>
+        <v>61.01335333333333</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2018993</v>
+        <v>2016798</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SRI ENTERPRISES</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>201178500076</v>
+        <v>200607201515</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B MART</t>
+          <t>LOW PRICE SUPER MARKET</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>56</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="G48" t="n">
-        <v>203.3141666666667</v>
+        <v>22.38210666666667</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2018993</v>
+        <v>2016798</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SRI ENTERPRISES</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>201178500087</v>
+        <v>200607201647</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>V MART SUPER MARKET</t>
+          <t>CHOICE SUPER MARKET</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>25</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="G49" t="n">
-        <v>53.99136000000001</v>
+        <v>42.01725999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2022679</v>
+        <v>2016798</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shree Kulswamini Enterprises</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>201294400165</v>
+        <v>200607201777</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B MART SUPER MARKET</t>
+          <t>CHAUDHARY MART</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ROHAN SINGH</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="G50" t="n">
-        <v>122.0849566666667</v>
+        <v>16.07479333333333</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2022679</v>
+        <v>2022988</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Shree Kulswamini Enterprises</t>
+          <t>VEDAVIT MARKETING ICE</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>201294400279</v>
+        <v>200654100179</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BALAJI FRESH MART</t>
+          <t>BABULAL D. CHOUDHARY KIRANA GENRAL STORE</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ROHAN SINGH</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>78.66666666666667</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="G51" t="n">
-        <v>96.27256333333332</v>
+        <v>43.26940333333334</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2022679</v>
+        <v>2009155</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Shree Kulswamini Enterprises</t>
+          <t>BABULAL JAYANTILAL &amp; CO.</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>201294400281</v>
+        <v>200915501263</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SHREE BALAJI FOOD MALL</t>
+          <t>DAIMOND MEDICAL  GEN STORE *</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ROHAN SINGH</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>73.66666666666667</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="G52" t="n">
-        <v>144.5002333333333</v>
+        <v>23.86577333333333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2022679</v>
+        <v>2009155</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shree Kulswamini Enterprises</t>
+          <t>BABULAL JAYANTILAL &amp; CO.</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>201294400288</v>
+        <v>200915501272</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B MART SUPER MARKET  (2)</t>
+          <t>TEMPTATIONS BAKERY  PATISSERIE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ROHAN SINGH</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>78.33333333333333</v>
+        <v>48.33333333333334</v>
       </c>
       <c r="G53" t="n">
-        <v>92.42781000000001</v>
+        <v>77.26626</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2022939</v>
+        <v>2009155</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>BABULAL JAYANTILAL &amp; CO.</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>201327000069</v>
+        <v>200915501283</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PATEL KIRANA AND GENERAL STORES</t>
+          <t>MEGA  MART</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>16.33333333333333</v>
+        <v>29.66666666666667</v>
       </c>
       <c r="G54" t="n">
-        <v>119.0924233333333</v>
+        <v>49.26277</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2022939</v>
+        <v>2009155</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>BABULAL JAYANTILAL &amp; CO.</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>201327000073</v>
+        <v>200915501320</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TOWN BAZAAR</t>
+          <t>SVK ENTERPRISES *</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>28.33333333333333</v>
+        <v>32.33333333333334</v>
       </c>
       <c r="G55" t="n">
-        <v>55.73072666666667</v>
+        <v>51.43595333333332</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2022939</v>
+        <v>2009155</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>BABULAL JAYANTILAL &amp; CO.</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>201327000332</v>
+        <v>200915501362</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ASHAPURA MART</t>
+          <t>MADHUR SUPER MARKET</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>41</v>
+        <v>36.33333333333334</v>
       </c>
       <c r="G56" t="n">
-        <v>62.44824333333333</v>
+        <v>106.3497633333333</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2022939</v>
+        <v>2022962</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>VEDAVIT MARKETING</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>201327000363</v>
+        <v>200989500689</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FINE FOOD BAZAAR</t>
+          <t>GIRNAR SUPER MARKET</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>51.66666666666666</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="G57" t="n">
-        <v>117.2941466666667</v>
+        <v>29.75330333333333</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2022639</v>
+        <v>2022962</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Shivani Enterprises</t>
+          <t>VEDAVIT MARKETING</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>201330600206</v>
+        <v>200989500714</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SAHAJANAND SUPER MARKET</t>
+          <t>SURYA ENTERPRISE</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JOSHUA SHAJI FRANCIS</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>26.33333333333333</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="G58" t="n">
-        <v>28.85700666666667</v>
+        <v>31.93960666666667</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2023671</v>
+        <v>2016798</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Shamik Enterprises</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>201330600340</v>
+        <v>200989501376</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B MART</t>
+          <t>PREM SUPER MARKET</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JOSHUA SHAJI FRANCIS</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>30.66666666666667</v>
       </c>
       <c r="G59" t="n">
-        <v>102.2013766666667</v>
+        <v>14.02102333333333</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2022939</v>
+        <v>2010080</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>Aakruti Agency</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>201330600476</v>
+        <v>201008000290</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SHIVAM ENTERPRISES</t>
+          <t>MOUNT VIEW SUPER MARKET</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>45.66666666666666</v>
+        <v>36</v>
       </c>
       <c r="G60" t="n">
-        <v>117.4925266666667</v>
+        <v>65.54219666666667</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2018993</v>
+        <v>2022962</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SRI ENTERPRISES</t>
+          <t>VEDAVIT MARKETING</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>201613300250</v>
+        <v>201119900003</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SHREEHARI ENTERPRISES APNA BAZAR CO-OP</t>
+          <t>Sahani Chemist  Super Mkt.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>30</v>
+        <v>28.66666666666667</v>
       </c>
       <c r="G61" t="n">
-        <v>38.00519666666667</v>
+        <v>34.98809333333333</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2018993</v>
+        <v>2011866</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SRI ENTERPRISES</t>
+          <t>Sainath Enterprises</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>201613300337</v>
+        <v>201186600256</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>A MART</t>
+          <t>FARMACY SUPAR STORE</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>40.33333333333334</v>
+        <v>54</v>
       </c>
       <c r="G62" t="n">
-        <v>114.82037</v>
+        <v>74.91144</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2023671</v>
+        <v>2011866</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Shamik Enterprises</t>
+          <t>Sainath Enterprises</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>201624800468</v>
+        <v>201186600264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KAVYA SUPER MARKET</t>
+          <t>M MART</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>JOSHUA SHAJI FRANCIS</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>12</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="G63" t="n">
-        <v>16.55300666666666</v>
+        <v>61.67669000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2023671</v>
+        <v>2011866</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Shamik Enterprises</t>
+          <t>Sainath Enterprises</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>201624800522</v>
+        <v>201186600286</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BALAJI MART</t>
+          <t>Quanto kisan private limited</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>JOSHUA SHAJI FRANCIS</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>40.33333333333334</v>
+        <v>64.66666666666667</v>
       </c>
       <c r="G64" t="n">
-        <v>80.87939</v>
+        <v>142.4468033333333</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2023085</v>
+        <v>2011866</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>N T Distributors</t>
+          <t>Sainath Enterprises</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>201636400069</v>
+        <v>201186600299</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>JASMINE SUPER MARKET FOOD BASKET</t>
+          <t>NEW V CARE MEDICO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UDAY DILIP INDALKAR</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>51.33333333333334</v>
+        <v>48.33333333333334</v>
       </c>
       <c r="G65" t="n">
-        <v>66.39796</v>
+        <v>76.86860333333333</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
+      <c r="A66" t="n">
+        <v>2016798</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SANVI DISTRIBUTORS</t>
+        </is>
+      </c>
       <c r="C66" t="n">
-        <v>201740900008</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+        <v>201679800043</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MATESHWARI KIRANA  GEN. STORES</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
+        </is>
+      </c>
       <c r="F66" t="n">
-        <v>2.333333333333333</v>
+        <v>20</v>
       </c>
       <c r="G66" t="n">
-        <v>16.47692</v>
+        <v>19.62726333333334</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2022939</v>
+        <v>2016798</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>201899300053</v>
+        <v>201679800048</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NEELKANTH FINE FOODS</t>
+          <t>GRAHAK SEVA MART</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>27.33333333333333</v>
+        <v>31</v>
       </c>
       <c r="G67" t="n">
-        <v>52.21021666666667</v>
+        <v>20.82142333333333</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2022939</v>
+        <v>2016798</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>201899300223</v>
+        <v>201679800146</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Shivam supar Market</t>
+          <t>RIDHI SUPER MARKET</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>20.66666666666667</v>
+        <v>27</v>
       </c>
       <c r="G68" t="n">
-        <v>32.73071333333333</v>
+        <v>142.2468933333333</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2022939</v>
+        <v>2016798</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>201899300414</v>
+        <v>201679800336</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Shiv super market</t>
+          <t>LOW PRiCE 2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>43</v>
+        <v>40.33333333333334</v>
       </c>
       <c r="G69" t="n">
-        <v>95.73931666666665</v>
+        <v>46.678</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2023823</v>
+        <v>2016798</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ashtavinayak Agencies</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>202112500012</v>
+        <v>201679800358</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PATEL MART</t>
+          <t>ORANGE CHEMIST</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AMIT SANJEEV PANDEY</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>32.33333333333334</v>
+        <v>35</v>
       </c>
       <c r="G70" t="n">
-        <v>24.53345666666667</v>
+        <v>49.57389000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2021330</v>
+        <v>2016798</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sweta Enterprises Dairy</t>
+          <t>SANVI DISTRIBUTORS</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>202133000511</v>
+        <v>201679800519</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CUREWELL PHARMACY</t>
+          <t>PREM SUPER MARKET</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ROHAN SINGH</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>33.66666666666666</v>
+        <v>40.66666666666666</v>
       </c>
       <c r="G71" t="n">
-        <v>75.98127333333333</v>
+        <v>23.14712666666667</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2022639</v>
+        <v>2017198</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Shivani Enterprises</t>
+          <t>KEVIN ENTERPRISES (DAIRY)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>202263900079</v>
+        <v>201719800039</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PRINZ SUPERMARKET</t>
+          <t>Gokul Sweet $ FARSAN MART</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>JOSHUA SHAJI FRANCIS</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>43</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="G72" t="n">
-        <v>102.3624333333333</v>
+        <v>26.40460666666667</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2022939</v>
+        <v>2017198</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>KEVIN ENTERPRISES (DAIRY)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>202293900019</v>
+        <v>201719800142</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MAA MART</t>
+          <t>SHRI SHANTINATH TRADING</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>40.66666666666666</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="G73" t="n">
-        <v>82.78822</v>
+        <v>19.15752666666667</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2022939</v>
+        <v>2021259</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>WADEKAR TRADERS</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>202293900020</v>
+        <v>201724600054</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NEELKANTH ENTERPRISES</t>
+          <t>PATANJALI GENERAL STORES</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>24.33333333333333</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="G74" t="n">
-        <v>36.97863</v>
+        <v>8.354963333333332</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2023085</v>
+        <v>2021259</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>N T Distributors</t>
+          <t>WADEKAR TRADERS</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>202308500082</v>
+        <v>201724600254</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>shiv krishna dairy</t>
+          <t>SAI GODAWARI MILK</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UDAY DILIP INDALKAR</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>14.66666666666667</v>
+        <v>9</v>
       </c>
       <c r="G75" t="n">
-        <v>27.27785333333334</v>
+        <v>20.12164666666667</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2023177</v>
+        <v>2021259</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Maxx Distributors</t>
+          <t>WADEKAR TRADERS</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>202317700011</v>
+        <v>201724600289</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Ashapura Super Market</t>
+          <t>MAHADEV SUPERMARKET</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>19</v>
+        <v>37.33333333333334</v>
       </c>
       <c r="G76" t="n">
-        <v>26.15719333333334</v>
+        <v>29.27486</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2023177</v>
+        <v>2021259</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Maxx Distributors</t>
+          <t>WADEKAR TRADERS</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>202317700022</v>
+        <v>201724600559</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Balaji Super Market</t>
+          <t>Momaiya Low Price (Dhanya Bazar)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>DARRYL PATRICK LOPES</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>22.66666666666667</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="G77" t="n">
-        <v>27.17055</v>
+        <v>78.17145666666667</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2023177</v>
+        <v>2022962</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Maxx Distributors</t>
+          <t>VEDAVIT MARKETING</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>202317700044</v>
+        <v>201742500140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Bhavani General Store</t>
+          <t>BALAJI SUPERMARKET</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>ARISON SEBESTIAN ALMEIDA</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G78" t="n">
-        <v>51.07444</v>
+        <v>27.82864</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2023177</v>
+        <v>2011866</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Maxx Distributors</t>
+          <t>Sainath Enterprises</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>202317700120</v>
+        <v>201759700166</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Jai Ambe Dry Fruit</t>
+          <t>BHAWANI MART</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>23.66666666666667</v>
+        <v>40</v>
       </c>
       <c r="G79" t="n">
-        <v>67.07551000000001</v>
+        <v>37.19241333333333</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2023177</v>
+        <v>2011866</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Maxx Distributors</t>
+          <t>Sainath Enterprises</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>202317700141</v>
+        <v>201759700242</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mamta Deiry  gen store</t>
+          <t>JODHPUR SUPERMARKET</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>VINAYAK VIJAY PATIL</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>23.66666666666667</v>
+        <v>39</v>
       </c>
       <c r="G80" t="n">
-        <v>45.96094666666666</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>2023823</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Ashtavinayak Agencies</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>202382300072</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>RAJENDRA SALES</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AMIT SANJEEV PANDEY</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>4.333333333333333</v>
-      </c>
-      <c r="G81" t="n">
-        <v>14.04947</v>
+        <v>43.71308666666666</v>
       </c>
     </row>
   </sheetData>
